--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>75</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>16/08 17:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>07/08 16:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>08/08 22:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/08 12:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>13/08 00:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>60</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>60</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>15/08 17:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>16/08 19:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>16/08 00:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>08/08 15:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>11/08 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>40</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.25</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>12/08 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>55</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45876.08459652701</v>
+        <v>45876.08459652778</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+7,51%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45876.08459652778</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Union Magd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Union Magdalena – AD PastoPrimera A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>07/08 23:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+18,8%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45876.1715467831</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – S</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gremio – Sport RecifeSérie A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10/08 23:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+7,51%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45876.08459652701</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,00%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+9,77%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45876.1715467831</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>07/08 23:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>50</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45876.1715467831</v>
+        <v>45876.17154678241</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45876.1715467831</v>
+        <v>45876.17154678241</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 17.5 - tirs1re équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Anderlecht – FC Sheriff TiraspolLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 17.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45876.22986402422</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45876.22986402422</v>
+        <v>45876.22986402778</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | J.Fonseca </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>J.Fonseca – Y.BuATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>07/08 15:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45876.27619005727</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | B.Bonzi – </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B.Bonzi – M.ArnaldiATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>07/08 15:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+9,45%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45876.27619005727</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>07/08 15:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45876.27619005727</v>
+        <v>45876.27619005787</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>07/08 15:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F31" t="n">
+        <v>2.4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,97 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45876.27619005727</v>
+        <v>45876.27619005787</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | R.Zarazua </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R.Zarazua – Y.PutintsevaWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>07/08 16:10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+29,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45876.31097172548</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Roman Safi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Roman Safiullin – Alejandro TabiloATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>07/08 16:10</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>73,0%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+9,44%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45876.31097172548</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>07/08 16:10</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45876.31097172548</v>
+        <v>45876.31097172454</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>07/08 16:10</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,232 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45876.31097172548</v>
+        <v>45876.31097172454</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FCSB – KF </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FCSB – KF DritaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>07/08 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+134%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45876.35674974333</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 22.5 - tirs | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – Legia VarsovieLigue Europa</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>07/08 16:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+38,2%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45876.35674974333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Jenson Bro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jenson Brooksby – Alexandre MullerATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>08/08 14:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>67,0%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+24,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45876.35674974333</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Benjamin B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi – Matteo ArnaldiATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>07/08 15:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45876.35674974333</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Joao Fonse</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Joao Fonseca – Yunchaokete BuATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>07/08 15:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45876.35674974333</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>07/08 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>150</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45876.35674974333</v>
+        <v>45876.35674974537</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>07/08 16:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45876.35674974333</v>
+        <v>45876.35674974537</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>08/08 14:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F36" t="n">
+        <v>1.85</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45876.35674974333</v>
+        <v>45876.35674974537</v>
       </c>
     </row>
     <row r="37">
@@ -2016,10 +2010,8 @@
           <t>07/08 15:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2032,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45876.35674974333</v>
+        <v>45876.35674974537</v>
       </c>
     </row>
     <row r="38">
@@ -2061,10 +2053,8 @@
           <t>07/08 15:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F38" t="n">
+        <v>1.9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2077,7 +2067,232 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45876.35674974333</v>
+        <v>45876.35674974537</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | V.Mboko – </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>V.Mboko – N.OsakaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>07/08 22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>70,2%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+29,9%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45876.39599540015</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Tristan Bo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tristan Boyer – Brandon HoltATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>08/08 14:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>51,4%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+28,6%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45876.39599540015</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 23.5 | J.Salisbur</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>J.Salisbury / N.Skupski – J.Cash / L.GlasspoolATP - Toronto, Doubles</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 23.5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>07/08 21:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>28,2%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+23,9%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45876.39599540015</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 1 | Javor – FK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Javor – FK Radnicki 1923Serbie - Serbie Super Liga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11/08 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45876.39599540015</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | Plus que 5.5 | AZ – FC Va</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AZ – FC VaduzLigue Europa Conférence - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45876.39599540015</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F39" t="n">
+        <v>1.85</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45876.39599540015</v>
+        <v>45876.3959954051</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>08/08 14:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45876.39599540015</v>
+        <v>45876.3959954051</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>07/08 21:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
+      <c r="F41" t="n">
+        <v>4.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45876.39599540015</v>
+        <v>45876.3959954051</v>
       </c>
     </row>
     <row r="42">
@@ -2231,10 +2225,8 @@
           <t>11/08 17:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
+      <c r="F42" t="n">
+        <v>4.82</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2247,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45876.39599540015</v>
+        <v>45876.3959954051</v>
       </c>
     </row>
     <row r="43">
@@ -2276,10 +2268,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2292,7 +2282,232 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45876.39599540015</v>
+        <v>45876.3959954051</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 24.5 | J.Salisbur</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>J.Salisbury / N.Skupski – J.Cash / L.GlasspoolATP - Toronto, Doubles</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 24.5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>07/08 21:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+46,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45876.43509581675</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 20.5 - tirs | CFR Cluj –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CFR Cluj – Sporting BragaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>07/08 16:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>56,3%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+42,4%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45876.43509581675</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – Legia VarsovieEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>07/08 16:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+32,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45876.43509581675</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | S.Cirstea </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>S.Cirstea – D.VekicWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>07/08 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+30,8%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45876.43509581675</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | R.Zarazua </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R.Zarazua – Y.PutintsevaWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>07/08 16:10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>61,1%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+22,1%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45876.43509581675</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>07/08 21:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
+      <c r="F44" t="n">
+        <v>5.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45876.43509581675</v>
+        <v>45876.43509582176</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>07/08 16:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.53</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45876.43509581675</v>
+        <v>45876.43509582176</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>07/08 16:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45876.43509581675</v>
+        <v>45876.43509582176</v>
       </c>
     </row>
     <row r="47">
@@ -2446,10 +2440,8 @@
           <t>07/08 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45876.43509581675</v>
+        <v>45876.43509582176</v>
       </c>
     </row>
     <row r="48">
@@ -2491,10 +2483,8 @@
           <t>07/08 16:10</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2507,7 +2497,142 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45876.43509581675</v>
+        <v>45876.43509582176</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sparta Prague – FC Ararat-ArmeniaEurope - Ligue  Conférence</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+14,3%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45876.47359229576</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>07/08 22:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45876.47359229576</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | C.Moutet –</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C.Moutet – M.McdonaldATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>07/08 23:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+9,90%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45876.47359229576</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>10</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45876.47359229576</v>
+        <v>45876.47359229167</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45876.47359229576</v>
+        <v>45876.47359229167</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>07/08 23:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,97 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45876.47359229576</v>
+        <v>45876.47359229167</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Anastasia </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Anastasia Potapova – Laura SiegemundWTA - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>07/08 17:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>71,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+7,70%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45876.53611315382</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Galway Uni</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Galway United – Shamrock RoversPremier Division</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10/08 16:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+7,55%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45876.53611315382</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>07/08 17:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45876.53611315382</v>
+        <v>45876.53611314815</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>10/08 16:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>40</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,97 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45876.53611315382</v>
+        <v>45876.53611314815</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | Pas de buts | Partizan B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Partizan Belgrade – HibernianLigue Europa Conférence - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>07/08 19:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+17,8%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45876.57136542038</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | Häcken – B</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Häcken – Brann-BergenEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>07/08 17:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45876.57136542038</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>14</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45876.57136542038</v>
+        <v>45876.57136541667</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>07/08 17:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.35</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,97 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45876.57136542038</v>
+        <v>45876.57136541667</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Estudiante</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata – Independiente RivadaviaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>08/08 00:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+47,1%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45876.60214872668</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – BreidablikLigue Europa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+19,2%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45876.60214872668</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>08/08 00:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>60</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45876.60214872668</v>
+        <v>45876.60214872685</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,52 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45876.60214872668</v>
+        <v>45876.60214872685</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Monterrey </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Monterrey – Mazatlan FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>17/08 15:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+37,0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45876.64416061462</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>60</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,52 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45876.64416061462</v>
+        <v>45876.64416061342</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | PAOK Salon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PAOK Salonique – Wolfsberger ACLigue Europa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>07/08 17:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45876.68909668621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,23 +2956,156 @@
           <t>07/08 17:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>55</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45876.68909668981</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gimnasia L</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17/08 17:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>+16,1%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>45876.68909668621</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+30,8%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45876.72544469517</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – Newell's Old BoysLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>17/08 17:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45876.72544469517</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 7.5 - tir cadré | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Maccabi HaifaLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>07/08 19:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>33,8%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+8,22%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45876.72544469517</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45876.72544469517</v>
+        <v>45876.72544469908</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>50</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45876.72544469517</v>
+        <v>45876.72544469908</v>
       </c>
     </row>
     <row r="62">
@@ -3089,10 +3085,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3.2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3105,7 +3099,97 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45876.72544469517</v>
+        <v>45876.72544469908</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 22.5 - tirs | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Maccabi HaifaLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>07/08 19:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+20,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45876.77536839586</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EC Bahia – FluminenseSérie A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>10/08 00:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45876.77536839586</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -3128,10 +3128,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.85</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45876.77536839586</v>
+        <v>45876.7753683912</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>10/08 00:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>55</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45876.77536839586</v>
+        <v>45876.7753683912</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3188,6 +3188,51 @@
         <v>45876.7753683912</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Newell's O</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>09/08 00:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45876.88997227428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,23 +3214,111 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>45</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45876.88997226852</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Union Magd</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Union Magdalena – AD PastoPrimera A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>07/08 23:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45876.93351914908</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Slovan </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FC Slovan Liberec – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>+8,77%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>45876.88997227428</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+8,01%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45876.93351914908</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-07.xlsx
+++ b/data/valuebets_database_2025-08-07.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>07/08 23:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>65</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45876.93351914908</v>
+        <v>45876.93351914352</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>45</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45876.93351914908</v>
+        <v>45876.93351914352</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Las Palmas</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Las Palmas – FC AndorraLaLiga2 A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>17/08 19:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+8,19%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45876.97483242536</v>
       </c>
     </row>
   </sheetData>
